--- a/Cartographie Audit IT [PERSONAL]/Cartographie_Risques_IT_Complete_Correspondances.xlsx
+++ b/Cartographie Audit IT [PERSONAL]/Cartographie_Risques_IT_Complete_Correspondances.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eleve04\Documents\Github\ProjetGithub\PROJECTS_NDOUDI_Nimrod\Cartographie Audit IT [PERSONAL]\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B55E3B10-08C7-4DCB-AF61-218D27ABF9B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48D9067C-471D-47BA-9D1B-EC8567E9A446}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -962,6 +962,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -1304,15 +1305,6 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1333,6 +1325,15 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1650,7 +1651,7 @@
     <col min="5" max="5" width="14.7109375" style="4" customWidth="1"/>
     <col min="6" max="6" width="16.7109375" style="5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="57" style="6" customWidth="1"/>
-    <col min="8" max="8" width="10.42578125" style="7" customWidth="1"/>
+    <col min="8" max="8" width="13.85546875" style="7" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12.140625" style="7" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="21.85546875" style="8" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="82.140625" style="2" customWidth="1"/>
@@ -1697,7 +1698,7 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="61" t="s">
         <v>11</v>
       </c>
       <c r="B2" s="18" t="s">
@@ -1733,7 +1734,7 @@
       <c r="L2" s="9"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="42"/>
+      <c r="A3" s="62"/>
       <c r="B3" s="25" t="s">
         <v>19</v>
       </c>
@@ -1766,7 +1767,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="42"/>
+      <c r="A4" s="62"/>
       <c r="B4" s="25" t="s">
         <v>26</v>
       </c>
@@ -1799,7 +1800,7 @@
       </c>
     </row>
     <row r="5" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="43"/>
+      <c r="A5" s="63"/>
       <c r="B5" s="32" t="s">
         <v>33</v>
       </c>
@@ -1832,7 +1833,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="41" t="s">
+      <c r="A6" s="61" t="s">
         <v>40</v>
       </c>
       <c r="B6" s="18" t="s">
@@ -1867,7 +1868,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="42"/>
+      <c r="A7" s="62"/>
       <c r="B7" s="25" t="s">
         <v>48</v>
       </c>
@@ -1900,7 +1901,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="42"/>
+      <c r="A8" s="62"/>
       <c r="B8" s="25" t="s">
         <v>55</v>
       </c>
@@ -1933,7 +1934,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="43"/>
+      <c r="A9" s="63"/>
       <c r="B9" s="32" t="s">
         <v>61</v>
       </c>
@@ -1966,7 +1967,7 @@
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="41" t="s">
+      <c r="A10" s="61" t="s">
         <v>67</v>
       </c>
       <c r="B10" s="18" t="s">
@@ -2001,7 +2002,7 @@
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" s="42"/>
+      <c r="A11" s="62"/>
       <c r="B11" s="25" t="s">
         <v>75</v>
       </c>
@@ -2034,7 +2035,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" s="42"/>
+      <c r="A12" s="62"/>
       <c r="B12" s="25" t="s">
         <v>82</v>
       </c>
@@ -2067,7 +2068,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="43"/>
+      <c r="A13" s="63"/>
       <c r="B13" s="32" t="s">
         <v>89</v>
       </c>
@@ -2100,7 +2101,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="41" t="s">
+      <c r="A14" s="61" t="s">
         <v>96</v>
       </c>
       <c r="B14" s="18" t="s">
@@ -2135,7 +2136,7 @@
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" s="42"/>
+      <c r="A15" s="62"/>
       <c r="B15" s="25" t="s">
         <v>104</v>
       </c>
@@ -2168,7 +2169,7 @@
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="42"/>
+      <c r="A16" s="62"/>
       <c r="B16" s="25" t="s">
         <v>109</v>
       </c>
@@ -2201,7 +2202,7 @@
       </c>
     </row>
     <row r="17" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="43"/>
+      <c r="A17" s="63"/>
       <c r="B17" s="32" t="s">
         <v>116</v>
       </c>
@@ -2234,7 +2235,7 @@
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A18" s="41" t="s">
+      <c r="A18" s="61" t="s">
         <v>120</v>
       </c>
       <c r="B18" s="18" t="s">
@@ -2269,7 +2270,7 @@
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A19" s="42"/>
+      <c r="A19" s="62"/>
       <c r="B19" s="25" t="s">
         <v>128</v>
       </c>
@@ -2302,7 +2303,7 @@
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A20" s="42"/>
+      <c r="A20" s="62"/>
       <c r="B20" s="25" t="s">
         <v>135</v>
       </c>
@@ -2335,7 +2336,7 @@
       </c>
     </row>
     <row r="21" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="43"/>
+      <c r="A21" s="63"/>
       <c r="B21" s="32" t="s">
         <v>142</v>
       </c>
@@ -2368,7 +2369,7 @@
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A22" s="41" t="s">
+      <c r="A22" s="61" t="s">
         <v>146</v>
       </c>
       <c r="B22" s="18" t="s">
@@ -2403,7 +2404,7 @@
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A23" s="42"/>
+      <c r="A23" s="62"/>
       <c r="B23" s="25" t="s">
         <v>154</v>
       </c>
@@ -2436,7 +2437,7 @@
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A24" s="42"/>
+      <c r="A24" s="62"/>
       <c r="B24" s="25" t="s">
         <v>159</v>
       </c>
@@ -2469,7 +2470,7 @@
       </c>
     </row>
     <row r="25" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="43"/>
+      <c r="A25" s="63"/>
       <c r="B25" s="32" t="s">
         <v>164</v>
       </c>
@@ -2502,7 +2503,7 @@
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A26" s="41" t="s">
+      <c r="A26" s="61" t="s">
         <v>169</v>
       </c>
       <c r="B26" s="18" t="s">
@@ -2537,7 +2538,7 @@
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A27" s="42"/>
+      <c r="A27" s="62"/>
       <c r="B27" s="25" t="s">
         <v>174</v>
       </c>
@@ -2570,7 +2571,7 @@
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A28" s="42"/>
+      <c r="A28" s="62"/>
       <c r="B28" s="25" t="s">
         <v>180</v>
       </c>
@@ -2603,7 +2604,7 @@
       </c>
     </row>
     <row r="29" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="43"/>
+      <c r="A29" s="63"/>
       <c r="B29" s="32" t="s">
         <v>186</v>
       </c>
@@ -2636,7 +2637,7 @@
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A30" s="42" t="s">
+      <c r="A30" s="62" t="s">
         <v>193</v>
       </c>
       <c r="B30" s="3" t="s">
@@ -2671,7 +2672,7 @@
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A31" s="42"/>
+      <c r="A31" s="62"/>
       <c r="B31" s="3" t="s">
         <v>201</v>
       </c>
@@ -2704,7 +2705,7 @@
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A32" s="42"/>
+      <c r="A32" s="62"/>
       <c r="B32" s="3" t="s">
         <v>205</v>
       </c>
@@ -2737,7 +2738,7 @@
       </c>
     </row>
     <row r="33" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="42"/>
+      <c r="A33" s="62"/>
       <c r="B33" s="3" t="s">
         <v>211</v>
       </c>
@@ -2770,7 +2771,7 @@
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A34" s="41" t="s">
+      <c r="A34" s="61" t="s">
         <v>215</v>
       </c>
       <c r="B34" s="18" t="s">
@@ -2805,7 +2806,7 @@
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A35" s="42"/>
+      <c r="A35" s="62"/>
       <c r="B35" s="25" t="s">
         <v>221</v>
       </c>
@@ -2838,7 +2839,7 @@
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A36" s="42"/>
+      <c r="A36" s="62"/>
       <c r="B36" s="25" t="s">
         <v>227</v>
       </c>
@@ -2871,7 +2872,7 @@
       </c>
     </row>
     <row r="37" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="43"/>
+      <c r="A37" s="63"/>
       <c r="B37" s="32" t="s">
         <v>233</v>
       </c>
@@ -2904,7 +2905,7 @@
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A38" s="41" t="s">
+      <c r="A38" s="61" t="s">
         <v>237</v>
       </c>
       <c r="B38" s="18" t="s">
@@ -2939,7 +2940,7 @@
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A39" s="42"/>
+      <c r="A39" s="62"/>
       <c r="B39" s="25" t="s">
         <v>243</v>
       </c>
@@ -2972,7 +2973,7 @@
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A40" s="42"/>
+      <c r="A40" s="62"/>
       <c r="B40" s="25" t="s">
         <v>250</v>
       </c>
@@ -3005,7 +3006,7 @@
       </c>
     </row>
     <row r="41" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="43"/>
+      <c r="A41" s="63"/>
       <c r="B41" s="32" t="s">
         <v>256</v>
       </c>
@@ -3067,189 +3068,189 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="45" t="s">
+      <c r="B1" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="46" t="s">
+      <c r="C1" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="47" t="s">
+      <c r="D1" s="44" t="s">
         <v>260</v>
       </c>
-      <c r="E1" s="63" t="s">
+      <c r="E1" s="60" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="58" t="s">
+      <c r="A2" s="55" t="s">
         <v>261</v>
       </c>
-      <c r="B2" s="59" t="s">
+      <c r="B2" s="56" t="s">
         <v>262</v>
       </c>
-      <c r="C2" s="60" t="s">
+      <c r="C2" s="57" t="s">
         <v>263</v>
       </c>
-      <c r="D2" s="61" t="s">
+      <c r="D2" s="58" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="62" t="s">
+      <c r="E2" s="59" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="48" t="s">
+      <c r="A3" s="45" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="50" t="s">
+      <c r="B3" s="47" t="s">
         <v>265</v>
       </c>
-      <c r="C3" s="52" t="s">
+      <c r="C3" s="49" t="s">
         <v>266</v>
       </c>
-      <c r="D3" s="54" t="s">
+      <c r="D3" s="51" t="s">
         <v>267</v>
       </c>
-      <c r="E3" s="56" t="s">
+      <c r="E3" s="53" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="48" t="s">
+      <c r="A4" s="45" t="s">
         <v>67</v>
       </c>
-      <c r="B4" s="50" t="s">
+      <c r="B4" s="47" t="s">
         <v>269</v>
       </c>
-      <c r="C4" s="52" t="s">
+      <c r="C4" s="49" t="s">
         <v>270</v>
       </c>
-      <c r="D4" s="54" t="s">
+      <c r="D4" s="51" t="s">
         <v>271</v>
       </c>
-      <c r="E4" s="56" t="s">
+      <c r="E4" s="53" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="48" t="s">
+      <c r="A5" s="45" t="s">
         <v>96</v>
       </c>
-      <c r="B5" s="50" t="s">
+      <c r="B5" s="47" t="s">
         <v>273</v>
       </c>
-      <c r="C5" s="52" t="s">
+      <c r="C5" s="49" t="s">
         <v>274</v>
       </c>
-      <c r="D5" s="54" t="s">
+      <c r="D5" s="51" t="s">
         <v>275</v>
       </c>
-      <c r="E5" s="56" t="s">
+      <c r="E5" s="53" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="48" t="s">
+      <c r="A6" s="45" t="s">
         <v>277</v>
       </c>
-      <c r="B6" s="50" t="s">
+      <c r="B6" s="47" t="s">
         <v>278</v>
       </c>
-      <c r="C6" s="52" t="s">
+      <c r="C6" s="49" t="s">
         <v>279</v>
       </c>
-      <c r="D6" s="54" t="s">
+      <c r="D6" s="51" t="s">
         <v>280</v>
       </c>
-      <c r="E6" s="56" t="s">
+      <c r="E6" s="53" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="48" t="s">
+      <c r="A7" s="45" t="s">
         <v>282</v>
       </c>
-      <c r="B7" s="50" t="s">
+      <c r="B7" s="47" t="s">
         <v>283</v>
       </c>
-      <c r="C7" s="52" t="s">
+      <c r="C7" s="49" t="s">
         <v>279</v>
       </c>
-      <c r="D7" s="54" t="s">
+      <c r="D7" s="51" t="s">
         <v>284</v>
       </c>
-      <c r="E7" s="56" t="s">
+      <c r="E7" s="53" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="48" t="s">
+      <c r="A8" s="45" t="s">
         <v>286</v>
       </c>
-      <c r="B8" s="50" t="s">
+      <c r="B8" s="47" t="s">
         <v>287</v>
       </c>
-      <c r="C8" s="52" t="s">
+      <c r="C8" s="49" t="s">
         <v>288</v>
       </c>
-      <c r="D8" s="54" t="s">
+      <c r="D8" s="51" t="s">
         <v>289</v>
       </c>
-      <c r="E8" s="56" t="s">
+      <c r="E8" s="53" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="48" t="s">
+      <c r="A9" s="45" t="s">
         <v>291</v>
       </c>
-      <c r="B9" s="50" t="s">
+      <c r="B9" s="47" t="s">
         <v>292</v>
       </c>
-      <c r="C9" s="52" t="s">
+      <c r="C9" s="49" t="s">
         <v>293</v>
       </c>
-      <c r="D9" s="54" t="s">
+      <c r="D9" s="51" t="s">
         <v>294</v>
       </c>
-      <c r="E9" s="56" t="s">
+      <c r="E9" s="53" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="48" t="s">
+      <c r="A10" s="45" t="s">
         <v>296</v>
       </c>
-      <c r="B10" s="50" t="s">
+      <c r="B10" s="47" t="s">
         <v>297</v>
       </c>
-      <c r="C10" s="52" t="s">
+      <c r="C10" s="49" t="s">
         <v>298</v>
       </c>
-      <c r="D10" s="54" t="s">
+      <c r="D10" s="51" t="s">
         <v>299</v>
       </c>
-      <c r="E10" s="56" t="s">
+      <c r="E10" s="53" t="s">
         <v>300</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="49" t="s">
+      <c r="A11" s="46" t="s">
         <v>237</v>
       </c>
-      <c r="B11" s="51" t="s">
+      <c r="B11" s="48" t="s">
         <v>301</v>
       </c>
-      <c r="C11" s="53" t="s">
+      <c r="C11" s="50" t="s">
         <v>302</v>
       </c>
-      <c r="D11" s="55" t="s">
+      <c r="D11" s="52" t="s">
         <v>303</v>
       </c>
-      <c r="E11" s="57" t="s">
+      <c r="E11" s="54" t="s">
         <v>304</v>
       </c>
     </row>
